--- a/src/test/output_test/Over_counts_regions/Region_over_0_10/Files/1.xlsx
+++ b/src/test/output_test/Over_counts_regions/Region_over_0_10/Files/1.xlsx
@@ -377,7 +377,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B188"/>
+  <dimension ref="A1:B201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -393,7 +393,7 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>327</v>
+        <v>311</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -401,7 +401,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -409,7 +409,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>364</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -417,7 +417,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>401</v>
+        <v>365</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -425,7 +425,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>404</v>
+        <v>414</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -433,7 +433,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>417</v>
+        <v>448</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -441,7 +441,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>463</v>
+        <v>456</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -449,7 +449,7 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>447</v>
+        <v>466</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -457,7 +457,7 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>496</v>
+        <v>493</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -465,7 +465,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>522</v>
+        <v>516</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -473,7 +473,7 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>552</v>
+        <v>536</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -481,7 +481,7 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>592</v>
+        <v>586</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -489,7 +489,7 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>611</v>
+        <v>628</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -497,7 +497,7 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>626</v>
+        <v>622</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -505,7 +505,7 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>633</v>
+        <v>671</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -513,7 +513,7 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>665</v>
+        <v>672</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -521,7 +521,7 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -529,7 +529,7 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>732</v>
+        <v>735</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -537,7 +537,7 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>741</v>
+        <v>710</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -545,7 +545,7 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>765</v>
+        <v>771</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -553,7 +553,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>790</v>
+        <v>758</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -561,7 +561,7 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>815</v>
+        <v>807</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -569,7 +569,7 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>837</v>
+        <v>848</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -577,7 +577,7 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>855</v>
+        <v>883</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -593,7 +593,7 @@
         <v>26</v>
       </c>
       <c r="B27">
-        <v>882</v>
+        <v>930</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -601,7 +601,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>915</v>
+        <v>909</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -609,7 +609,7 @@
         <v>28</v>
       </c>
       <c r="B29">
-        <v>895</v>
+        <v>893</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -617,7 +617,7 @@
         <v>29</v>
       </c>
       <c r="B30">
-        <v>883</v>
+        <v>967</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -625,7 +625,7 @@
         <v>30</v>
       </c>
       <c r="B31">
-        <v>950</v>
+        <v>979</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -633,7 +633,7 @@
         <v>31</v>
       </c>
       <c r="B32">
-        <v>935</v>
+        <v>989</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -641,7 +641,7 @@
         <v>32</v>
       </c>
       <c r="B33">
-        <v>962</v>
+        <v>968</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -649,7 +649,7 @@
         <v>33</v>
       </c>
       <c r="B34">
-        <v>1023</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -657,7 +657,7 @@
         <v>34</v>
       </c>
       <c r="B35">
-        <v>966</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -665,7 +665,7 @@
         <v>35</v>
       </c>
       <c r="B36">
-        <v>986</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -673,7 +673,7 @@
         <v>36</v>
       </c>
       <c r="B37">
-        <v>998</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -681,7 +681,7 @@
         <v>37</v>
       </c>
       <c r="B38">
-        <v>1065</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -689,7 +689,7 @@
         <v>38</v>
       </c>
       <c r="B39">
-        <v>1088</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -697,7 +697,7 @@
         <v>39</v>
       </c>
       <c r="B40">
-        <v>1070</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -705,7 +705,7 @@
         <v>40</v>
       </c>
       <c r="B41">
-        <v>1052</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -713,7 +713,7 @@
         <v>41</v>
       </c>
       <c r="B42">
-        <v>1082</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -721,7 +721,7 @@
         <v>42</v>
       </c>
       <c r="B43">
-        <v>1088</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -729,7 +729,7 @@
         <v>43</v>
       </c>
       <c r="B44">
-        <v>1027</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -737,7 +737,7 @@
         <v>44</v>
       </c>
       <c r="B45">
-        <v>1037</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -745,7 +745,7 @@
         <v>45</v>
       </c>
       <c r="B46">
-        <v>1058</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -753,7 +753,7 @@
         <v>46</v>
       </c>
       <c r="B47">
-        <v>1026</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -761,7 +761,7 @@
         <v>47</v>
       </c>
       <c r="B48">
-        <v>1091</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -769,7 +769,7 @@
         <v>48</v>
       </c>
       <c r="B49">
-        <v>1086</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -777,7 +777,7 @@
         <v>49</v>
       </c>
       <c r="B50">
-        <v>1086</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -785,7 +785,7 @@
         <v>50</v>
       </c>
       <c r="B51">
-        <v>1063</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -793,7 +793,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>1125</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -801,7 +801,7 @@
         <v>52</v>
       </c>
       <c r="B53">
-        <v>1058</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -809,7 +809,7 @@
         <v>53</v>
       </c>
       <c r="B54">
-        <v>1148</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -817,7 +817,7 @@
         <v>54</v>
       </c>
       <c r="B55">
-        <v>1047</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -825,7 +825,7 @@
         <v>55</v>
       </c>
       <c r="B56">
-        <v>1037</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -833,7 +833,7 @@
         <v>56</v>
       </c>
       <c r="B57">
-        <v>1017</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -841,7 +841,7 @@
         <v>57</v>
       </c>
       <c r="B58">
-        <v>1070</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -849,7 +849,7 @@
         <v>58</v>
       </c>
       <c r="B59">
-        <v>1032</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -857,7 +857,7 @@
         <v>59</v>
       </c>
       <c r="B60">
-        <v>1058</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -865,7 +865,7 @@
         <v>60</v>
       </c>
       <c r="B61">
-        <v>1075</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -873,7 +873,7 @@
         <v>61</v>
       </c>
       <c r="B62">
-        <v>1090</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -881,7 +881,7 @@
         <v>62</v>
       </c>
       <c r="B63">
-        <v>1010</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -889,7 +889,7 @@
         <v>63</v>
       </c>
       <c r="B64">
-        <v>998</v>
+        <v>987</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -897,7 +897,7 @@
         <v>64</v>
       </c>
       <c r="B65">
-        <v>973</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -905,7 +905,7 @@
         <v>65</v>
       </c>
       <c r="B66">
-        <v>1021</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -913,7 +913,7 @@
         <v>66</v>
       </c>
       <c r="B67">
-        <v>951</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -921,7 +921,7 @@
         <v>67</v>
       </c>
       <c r="B68">
-        <v>1008</v>
+        <v>944</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -929,7 +929,7 @@
         <v>68</v>
       </c>
       <c r="B69">
-        <v>981</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -937,7 +937,7 @@
         <v>69</v>
       </c>
       <c r="B70">
-        <v>978</v>
+        <v>932</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -945,7 +945,7 @@
         <v>70</v>
       </c>
       <c r="B71">
-        <v>908</v>
+        <v>927</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -953,7 +953,7 @@
         <v>71</v>
       </c>
       <c r="B72">
-        <v>941</v>
+        <v>949</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -961,7 +961,7 @@
         <v>72</v>
       </c>
       <c r="B73">
-        <v>960</v>
+        <v>950</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -969,7 +969,7 @@
         <v>73</v>
       </c>
       <c r="B74">
-        <v>856</v>
+        <v>904</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -977,7 +977,7 @@
         <v>74</v>
       </c>
       <c r="B75">
-        <v>912</v>
+        <v>896</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -985,7 +985,7 @@
         <v>75</v>
       </c>
       <c r="B76">
-        <v>843</v>
+        <v>901</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -993,7 +993,7 @@
         <v>76</v>
       </c>
       <c r="B77">
-        <v>847</v>
+        <v>912</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1001,7 +1001,7 @@
         <v>77</v>
       </c>
       <c r="B78">
-        <v>836</v>
+        <v>780</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1009,7 +1009,7 @@
         <v>78</v>
       </c>
       <c r="B79">
-        <v>843</v>
+        <v>818</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1017,7 +1017,7 @@
         <v>79</v>
       </c>
       <c r="B80">
-        <v>821</v>
+        <v>755</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1025,7 +1025,7 @@
         <v>80</v>
       </c>
       <c r="B81">
-        <v>793</v>
+        <v>757</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1033,7 +1033,7 @@
         <v>81</v>
       </c>
       <c r="B82">
-        <v>755</v>
+        <v>735</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -1041,7 +1041,7 @@
         <v>82</v>
       </c>
       <c r="B83">
-        <v>692</v>
+        <v>773</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -1049,7 +1049,7 @@
         <v>83</v>
       </c>
       <c r="B84">
-        <v>712</v>
+        <v>669</v>
       </c>
     </row>
     <row r="85" spans="1:2">
@@ -1057,7 +1057,7 @@
         <v>84</v>
       </c>
       <c r="B85">
-        <v>705</v>
+        <v>653</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -1065,7 +1065,7 @@
         <v>85</v>
       </c>
       <c r="B86">
-        <v>678</v>
+        <v>681</v>
       </c>
     </row>
     <row r="87" spans="1:2">
@@ -1073,7 +1073,7 @@
         <v>86</v>
       </c>
       <c r="B87">
-        <v>730</v>
+        <v>680</v>
       </c>
     </row>
     <row r="88" spans="1:2">
@@ -1081,7 +1081,7 @@
         <v>87</v>
       </c>
       <c r="B88">
-        <v>656</v>
+        <v>652</v>
       </c>
     </row>
     <row r="89" spans="1:2">
@@ -1089,7 +1089,7 @@
         <v>88</v>
       </c>
       <c r="B89">
-        <v>641</v>
+        <v>613</v>
       </c>
     </row>
     <row r="90" spans="1:2">
@@ -1097,7 +1097,7 @@
         <v>89</v>
       </c>
       <c r="B90">
-        <v>561</v>
+        <v>597</v>
       </c>
     </row>
     <row r="91" spans="1:2">
@@ -1105,7 +1105,7 @@
         <v>90</v>
       </c>
       <c r="B91">
-        <v>567</v>
+        <v>554</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -1113,7 +1113,7 @@
         <v>91</v>
       </c>
       <c r="B92">
-        <v>543</v>
+        <v>577</v>
       </c>
     </row>
     <row r="93" spans="1:2">
@@ -1121,7 +1121,7 @@
         <v>92</v>
       </c>
       <c r="B93">
-        <v>546</v>
+        <v>523</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -1129,7 +1129,7 @@
         <v>93</v>
       </c>
       <c r="B94">
-        <v>537</v>
+        <v>479</v>
       </c>
     </row>
     <row r="95" spans="1:2">
@@ -1137,7 +1137,7 @@
         <v>94</v>
       </c>
       <c r="B95">
-        <v>483</v>
+        <v>513</v>
       </c>
     </row>
     <row r="96" spans="1:2">
@@ -1145,7 +1145,7 @@
         <v>95</v>
       </c>
       <c r="B96">
-        <v>472</v>
+        <v>501</v>
       </c>
     </row>
     <row r="97" spans="1:2">
@@ -1153,7 +1153,7 @@
         <v>96</v>
       </c>
       <c r="B97">
-        <v>444</v>
+        <v>476</v>
       </c>
     </row>
     <row r="98" spans="1:2">
@@ -1161,7 +1161,7 @@
         <v>97</v>
       </c>
       <c r="B98">
-        <v>411</v>
+        <v>456</v>
       </c>
     </row>
     <row r="99" spans="1:2">
@@ -1169,7 +1169,7 @@
         <v>98</v>
       </c>
       <c r="B99">
-        <v>447</v>
+        <v>415</v>
       </c>
     </row>
     <row r="100" spans="1:2">
@@ -1177,7 +1177,7 @@
         <v>99</v>
       </c>
       <c r="B100">
-        <v>389</v>
+        <v>404</v>
       </c>
     </row>
     <row r="101" spans="1:2">
@@ -1185,7 +1185,7 @@
         <v>100</v>
       </c>
       <c r="B101">
-        <v>400</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:2">
@@ -1193,7 +1193,7 @@
         <v>101</v>
       </c>
       <c r="B102">
-        <v>393</v>
+        <v>343</v>
       </c>
     </row>
     <row r="103" spans="1:2">
@@ -1201,7 +1201,7 @@
         <v>102</v>
       </c>
       <c r="B103">
-        <v>364</v>
+        <v>332</v>
       </c>
     </row>
     <row r="104" spans="1:2">
@@ -1209,7 +1209,7 @@
         <v>103</v>
       </c>
       <c r="B104">
-        <v>373</v>
+        <v>314</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -1217,7 +1217,7 @@
         <v>104</v>
       </c>
       <c r="B105">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="106" spans="1:2">
@@ -1225,7 +1225,7 @@
         <v>105</v>
       </c>
       <c r="B106">
-        <v>290</v>
+        <v>274</v>
       </c>
     </row>
     <row r="107" spans="1:2">
@@ -1233,7 +1233,7 @@
         <v>106</v>
       </c>
       <c r="B107">
-        <v>302</v>
+        <v>266</v>
       </c>
     </row>
     <row r="108" spans="1:2">
@@ -1241,7 +1241,7 @@
         <v>107</v>
       </c>
       <c r="B108">
-        <v>288</v>
+        <v>268</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -1249,7 +1249,7 @@
         <v>108</v>
       </c>
       <c r="B109">
-        <v>292</v>
+        <v>244</v>
       </c>
     </row>
     <row r="110" spans="1:2">
@@ -1257,7 +1257,7 @@
         <v>109</v>
       </c>
       <c r="B110">
-        <v>270</v>
+        <v>229</v>
       </c>
     </row>
     <row r="111" spans="1:2">
@@ -1265,7 +1265,7 @@
         <v>110</v>
       </c>
       <c r="B111">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -1273,7 +1273,7 @@
         <v>111</v>
       </c>
       <c r="B112">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="113" spans="1:2">
@@ -1281,7 +1281,7 @@
         <v>112</v>
       </c>
       <c r="B113">
-        <v>233</v>
+        <v>236</v>
       </c>
     </row>
     <row r="114" spans="1:2">
@@ -1289,7 +1289,7 @@
         <v>113</v>
       </c>
       <c r="B114">
-        <v>197</v>
+        <v>217</v>
       </c>
     </row>
     <row r="115" spans="1:2">
@@ -1297,7 +1297,7 @@
         <v>114</v>
       </c>
       <c r="B115">
-        <v>225</v>
+        <v>194</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -1305,7 +1305,7 @@
         <v>115</v>
       </c>
       <c r="B116">
-        <v>202</v>
+        <v>178</v>
       </c>
     </row>
     <row r="117" spans="1:2">
@@ -1313,7 +1313,7 @@
         <v>116</v>
       </c>
       <c r="B117">
-        <v>222</v>
+        <v>168</v>
       </c>
     </row>
     <row r="118" spans="1:2">
@@ -1321,7 +1321,7 @@
         <v>117</v>
       </c>
       <c r="B118">
-        <v>183</v>
+        <v>178</v>
       </c>
     </row>
     <row r="119" spans="1:2">
@@ -1329,7 +1329,7 @@
         <v>118</v>
       </c>
       <c r="B119">
-        <v>184</v>
+        <v>145</v>
       </c>
     </row>
     <row r="120" spans="1:2">
@@ -1337,7 +1337,7 @@
         <v>119</v>
       </c>
       <c r="B120">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="121" spans="1:2">
@@ -1345,7 +1345,7 @@
         <v>120</v>
       </c>
       <c r="B121">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
     <row r="122" spans="1:2">
@@ -1353,7 +1353,7 @@
         <v>121</v>
       </c>
       <c r="B122">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="123" spans="1:2">
@@ -1361,7 +1361,7 @@
         <v>122</v>
       </c>
       <c r="B123">
-        <v>147</v>
+        <v>131</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -1369,7 +1369,7 @@
         <v>123</v>
       </c>
       <c r="B124">
-        <v>145</v>
+        <v>134</v>
       </c>
     </row>
     <row r="125" spans="1:2">
@@ -1377,7 +1377,7 @@
         <v>124</v>
       </c>
       <c r="B125">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="126" spans="1:2">
@@ -1385,7 +1385,7 @@
         <v>125</v>
       </c>
       <c r="B126">
-        <v>118</v>
+        <v>92</v>
       </c>
     </row>
     <row r="127" spans="1:2">
@@ -1393,7 +1393,7 @@
         <v>126</v>
       </c>
       <c r="B127">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="128" spans="1:2">
@@ -1401,7 +1401,7 @@
         <v>127</v>
       </c>
       <c r="B128">
-        <v>102</v>
+        <v>110</v>
       </c>
     </row>
     <row r="129" spans="1:2">
@@ -1409,7 +1409,7 @@
         <v>128</v>
       </c>
       <c r="B129">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="130" spans="1:2">
@@ -1417,7 +1417,7 @@
         <v>129</v>
       </c>
       <c r="B130">
-        <v>114</v>
+        <v>87</v>
       </c>
     </row>
     <row r="131" spans="1:2">
@@ -1425,7 +1425,7 @@
         <v>130</v>
       </c>
       <c r="B131">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="132" spans="1:2">
@@ -1433,7 +1433,7 @@
         <v>131</v>
       </c>
       <c r="B132">
-        <v>100</v>
+        <v>67</v>
       </c>
     </row>
     <row r="133" spans="1:2">
@@ -1441,7 +1441,7 @@
         <v>132</v>
       </c>
       <c r="B133">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="134" spans="1:2">
@@ -1449,7 +1449,7 @@
         <v>133</v>
       </c>
       <c r="B134">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="135" spans="1:2">
@@ -1457,7 +1457,7 @@
         <v>134</v>
       </c>
       <c r="B135">
-        <v>105</v>
+        <v>73</v>
       </c>
     </row>
     <row r="136" spans="1:2">
@@ -1465,7 +1465,7 @@
         <v>135</v>
       </c>
       <c r="B136">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="137" spans="1:2">
@@ -1473,7 +1473,7 @@
         <v>136</v>
       </c>
       <c r="B137">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="138" spans="1:2">
@@ -1481,7 +1481,7 @@
         <v>137</v>
       </c>
       <c r="B138">
-        <v>67</v>
+        <v>85</v>
       </c>
     </row>
     <row r="139" spans="1:2">
@@ -1489,7 +1489,7 @@
         <v>138</v>
       </c>
       <c r="B139">
-        <v>76</v>
+        <v>65</v>
       </c>
     </row>
     <row r="140" spans="1:2">
@@ -1497,7 +1497,7 @@
         <v>139</v>
       </c>
       <c r="B140">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="141" spans="1:2">
@@ -1505,7 +1505,7 @@
         <v>140</v>
       </c>
       <c r="B141">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="142" spans="1:2">
@@ -1513,7 +1513,7 @@
         <v>141</v>
       </c>
       <c r="B142">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="143" spans="1:2">
@@ -1521,7 +1521,7 @@
         <v>142</v>
       </c>
       <c r="B143">
-        <v>52</v>
+        <v>62</v>
       </c>
     </row>
     <row r="144" spans="1:2">
@@ -1529,7 +1529,7 @@
         <v>143</v>
       </c>
       <c r="B144">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="145" spans="1:2">
@@ -1537,7 +1537,7 @@
         <v>144</v>
       </c>
       <c r="B145">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="146" spans="1:2">
@@ -1545,7 +1545,7 @@
         <v>145</v>
       </c>
       <c r="B146">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="147" spans="1:2">
@@ -1553,7 +1553,7 @@
         <v>146</v>
       </c>
       <c r="B147">
-        <v>61</v>
+        <v>51</v>
       </c>
     </row>
     <row r="148" spans="1:2">
@@ -1561,7 +1561,7 @@
         <v>147</v>
       </c>
       <c r="B148">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="149" spans="1:2">
@@ -1569,7 +1569,7 @@
         <v>148</v>
       </c>
       <c r="B149">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="150" spans="1:2">
@@ -1577,7 +1577,7 @@
         <v>149</v>
       </c>
       <c r="B150">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="151" spans="1:2">
@@ -1593,7 +1593,7 @@
         <v>151</v>
       </c>
       <c r="B152">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="153" spans="1:2">
@@ -1601,7 +1601,7 @@
         <v>152</v>
       </c>
       <c r="B153">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="154" spans="1:2">
@@ -1609,7 +1609,7 @@
         <v>153</v>
       </c>
       <c r="B154">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="155" spans="1:2">
@@ -1625,7 +1625,7 @@
         <v>155</v>
       </c>
       <c r="B156">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="157" spans="1:2">
@@ -1633,7 +1633,7 @@
         <v>156</v>
       </c>
       <c r="B157">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="158" spans="1:2">
@@ -1641,7 +1641,7 @@
         <v>157</v>
       </c>
       <c r="B158">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="159" spans="1:2">
@@ -1649,7 +1649,7 @@
         <v>158</v>
       </c>
       <c r="B159">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="160" spans="1:2">
@@ -1657,7 +1657,7 @@
         <v>159</v>
       </c>
       <c r="B160">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="161" spans="1:2">
@@ -1665,7 +1665,7 @@
         <v>160</v>
       </c>
       <c r="B161">
-        <v>42</v>
+        <v>23</v>
       </c>
     </row>
     <row r="162" spans="1:2">
@@ -1673,7 +1673,7 @@
         <v>161</v>
       </c>
       <c r="B162">
-        <v>29</v>
+        <v>21</v>
       </c>
     </row>
     <row r="163" spans="1:2">
@@ -1681,7 +1681,7 @@
         <v>162</v>
       </c>
       <c r="B163">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="164" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>164</v>
       </c>
       <c r="B165">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="166" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>165</v>
       </c>
       <c r="B166">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="167" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>166</v>
       </c>
       <c r="B167">
-        <v>19</v>
+        <v>29</v>
       </c>
     </row>
     <row r="168" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>167</v>
       </c>
       <c r="B168">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="169" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>168</v>
       </c>
       <c r="B169">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="170" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>169</v>
       </c>
       <c r="B170">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="171" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>170</v>
       </c>
       <c r="B171">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="172" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>171</v>
       </c>
       <c r="B172">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="173" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>172</v>
       </c>
       <c r="B173">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="174" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>173</v>
       </c>
       <c r="B174">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="175" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>174</v>
       </c>
       <c r="B175">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="176" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>175</v>
       </c>
       <c r="B176">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>176</v>
       </c>
       <c r="B177">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>177</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
     <row r="179" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>178</v>
       </c>
       <c r="B179">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="180" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>179</v>
       </c>
       <c r="B180">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="181" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>180</v>
       </c>
       <c r="B181">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="182" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>183</v>
       </c>
       <c r="B184">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -1881,6 +1881,110 @@
         <v>187</v>
       </c>
       <c r="B188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189">
+        <v>188</v>
+      </c>
+      <c r="B189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190">
+        <v>189</v>
+      </c>
+      <c r="B190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191">
+        <v>190</v>
+      </c>
+      <c r="B191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192">
+        <v>191</v>
+      </c>
+      <c r="B192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193">
+        <v>192</v>
+      </c>
+      <c r="B193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194">
+        <v>193</v>
+      </c>
+      <c r="B194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195">
+        <v>194</v>
+      </c>
+      <c r="B195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196">
+        <v>195</v>
+      </c>
+      <c r="B196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197">
+        <v>196</v>
+      </c>
+      <c r="B197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198">
+        <v>197</v>
+      </c>
+      <c r="B198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199">
+        <v>198</v>
+      </c>
+      <c r="B199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200">
+        <v>199</v>
+      </c>
+      <c r="B200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201">
+        <v>200</v>
+      </c>
+      <c r="B201">
         <v>12</v>
       </c>
     </row>
